--- a/public/template_advance.xlsx
+++ b/public/template_advance.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yeavm\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\backend\financial_project\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -162,7 +162,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -247,23 +247,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -320,48 +309,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -379,6 +326,48 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -712,48 +701,48 @@
     <col min="5" max="5" width="25.875" style="10" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="34" customWidth="1"/>
-    <col min="9" max="9" width="11" style="35"/>
+    <col min="8" max="8" width="19.375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="11" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="36"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="37"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:12" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
+      <c r="A3" s="31">
         <v>3</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="38"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" spans="1:12" ht="33" x14ac:dyDescent="0.7">
       <c r="A4" s="14" t="s">
@@ -817,87 +806,87 @@
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:12" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="36"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.7">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="26" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="25"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="26"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="25"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.7">
       <c r="A14" s="15"/>
@@ -906,7 +895,7 @@
       <c r="D14" s="17"/>
       <c r="E14" s="18"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="33"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.7">
@@ -1169,12 +1158,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="G11:G13"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="C11:C13"/>
@@ -1183,6 +1166,12 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
   </mergeCells>
   <conditionalFormatting sqref="F1:F13 F123:F1048576">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">

--- a/public/template_advance.xlsx
+++ b/public/template_advance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ក្រសួងការងារ និងបណ្ដុះបណ្ដាលវិជ្ជាជីវៈ</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>ស្ថានភាពឥណទានថ្មី</t>
-  </si>
-  <si>
-    <t>សមតុល្យដើមគ្រា</t>
   </si>
   <si>
     <t>អនុវត្ត</t>
@@ -326,6 +323,39 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -334,39 +364,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -691,7 +688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="7.875" style="11" customWidth="1"/>
@@ -700,51 +697,47 @@
     <col min="4" max="4" width="37.625" style="13" customWidth="1"/>
     <col min="5" max="5" width="25.875" style="10" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="20" customWidth="1"/>
-    <col min="9" max="9" width="11" style="21"/>
+    <col min="7" max="7" width="19.375" style="20" customWidth="1"/>
+    <col min="8" max="8" width="11" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="33" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="22"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="23"/>
-    </row>
-    <row r="3" spans="1:12" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="31">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="23"/>
+    </row>
+    <row r="3" spans="1:11" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="32">
         <v>3</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="24"/>
-    </row>
-    <row r="4" spans="1:12" ht="33" x14ac:dyDescent="0.7">
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="24"/>
+    </row>
+    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.7">
       <c r="A4" s="14" t="s">
         <v>0</v>
       </c>
@@ -754,10 +747,9 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" ht="33" x14ac:dyDescent="0.7">
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.7">
       <c r="A5" s="14" t="s">
         <v>1</v>
       </c>
@@ -767,10 +759,9 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" ht="33" x14ac:dyDescent="0.7">
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" ht="33" x14ac:dyDescent="0.7">
       <c r="A6" s="14" t="s">
         <v>2</v>
       </c>
@@ -780,10 +771,9 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" ht="33" x14ac:dyDescent="0.7">
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" ht="33" x14ac:dyDescent="0.7">
       <c r="A7" s="14"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
@@ -791,10 +781,9 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.7">
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
@@ -802,375 +791,365 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="22"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.7">
-      <c r="A10" s="39" t="s">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="A10" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="25"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
+    </row>
+    <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.7">
+    </row>
+    <row r="12" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.7">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="16"/>
       <c r="D14" s="17"/>
       <c r="E14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.7">
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.7">
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I19" s="11"/>
-    </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I23" s="11"/>
-    </row>
-    <row r="24" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I24" s="11"/>
-    </row>
-    <row r="25" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I25" s="11"/>
-    </row>
-    <row r="26" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I26" s="11"/>
-    </row>
-    <row r="27" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I27" s="11"/>
-    </row>
-    <row r="28" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I28" s="11"/>
-    </row>
-    <row r="29" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I29" s="11"/>
-    </row>
-    <row r="30" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I30" s="11"/>
-    </row>
-    <row r="31" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I31" s="11"/>
-    </row>
-    <row r="32" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I33" s="11"/>
-    </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I34" s="11"/>
-    </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I35" s="11"/>
-    </row>
-    <row r="36" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I36" s="11"/>
-    </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I37" s="11"/>
-    </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I38" s="11"/>
-    </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I39" s="11"/>
-    </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I40" s="11"/>
-    </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I41" s="11"/>
-    </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I42" s="11"/>
-    </row>
-    <row r="43" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I43" s="11"/>
-    </row>
-    <row r="44" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I44" s="11"/>
-    </row>
-    <row r="45" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I45" s="11"/>
-    </row>
-    <row r="46" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I46" s="11"/>
-    </row>
-    <row r="47" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I47" s="11"/>
-    </row>
-    <row r="48" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I48" s="11"/>
-    </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I49" s="11"/>
-    </row>
-    <row r="50" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I50" s="11"/>
-    </row>
-    <row r="51" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I51" s="11"/>
-    </row>
-    <row r="52" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I52" s="11"/>
-    </row>
-    <row r="53" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I53" s="11"/>
-    </row>
-    <row r="54" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I54" s="11"/>
-    </row>
-    <row r="55" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I55" s="11"/>
-    </row>
-    <row r="56" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I56" s="11"/>
-    </row>
-    <row r="57" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I57" s="11"/>
-    </row>
-    <row r="58" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I58" s="11"/>
-    </row>
-    <row r="59" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I59" s="11"/>
-    </row>
-    <row r="60" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I60" s="11"/>
-    </row>
-    <row r="61" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I61" s="11"/>
-    </row>
-    <row r="62" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I62" s="11"/>
-    </row>
-    <row r="63" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I63" s="11"/>
-    </row>
-    <row r="64" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I64" s="11"/>
-    </row>
-    <row r="65" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I65" s="11"/>
-    </row>
-    <row r="66" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I66" s="11"/>
-    </row>
-    <row r="67" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I67" s="11"/>
-    </row>
-    <row r="68" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I68" s="11"/>
-    </row>
-    <row r="69" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I69" s="11"/>
-    </row>
-    <row r="70" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I70" s="11"/>
-    </row>
-    <row r="71" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I71" s="11"/>
-    </row>
-    <row r="72" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I72" s="11"/>
-    </row>
-    <row r="73" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I73" s="11"/>
-    </row>
-    <row r="74" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I74" s="11"/>
-    </row>
-    <row r="75" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I75" s="11"/>
-    </row>
-    <row r="76" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I76" s="11"/>
-    </row>
-    <row r="77" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I77" s="11"/>
-    </row>
-    <row r="78" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I78" s="11"/>
-    </row>
-    <row r="79" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I79" s="11"/>
-    </row>
-    <row r="80" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I80" s="11"/>
-    </row>
-    <row r="81" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I81" s="11"/>
-    </row>
-    <row r="82" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I82" s="11"/>
-    </row>
-    <row r="83" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I83" s="11"/>
-    </row>
-    <row r="84" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I84" s="11"/>
-    </row>
-    <row r="85" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I85" s="11"/>
-    </row>
-    <row r="86" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I86" s="11"/>
-    </row>
-    <row r="87" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I87" s="11"/>
-    </row>
-    <row r="88" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I88" s="11"/>
-    </row>
-    <row r="89" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I89" s="11"/>
-    </row>
-    <row r="90" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I90" s="11"/>
-    </row>
-    <row r="91" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I91" s="11"/>
-    </row>
-    <row r="92" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I92" s="11"/>
-    </row>
-    <row r="93" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I93" s="11"/>
-    </row>
-    <row r="94" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I94" s="11"/>
-    </row>
-    <row r="95" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I95" s="11"/>
-    </row>
-    <row r="96" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I96" s="11"/>
-    </row>
-    <row r="97" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I97" s="11"/>
-    </row>
-    <row r="98" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I98" s="11"/>
-    </row>
-    <row r="99" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I99" s="11"/>
-    </row>
-    <row r="100" spans="9:9" x14ac:dyDescent="0.7">
-      <c r="I100" s="11"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H22" s="11"/>
+    </row>
+    <row r="23" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H23" s="11"/>
+    </row>
+    <row r="24" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H24" s="11"/>
+    </row>
+    <row r="25" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H25" s="11"/>
+    </row>
+    <row r="26" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H31" s="11"/>
+    </row>
+    <row r="32" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H32" s="11"/>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H33" s="11"/>
+    </row>
+    <row r="34" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H34" s="11"/>
+    </row>
+    <row r="35" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H35" s="11"/>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H36" s="11"/>
+    </row>
+    <row r="37" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H37" s="11"/>
+    </row>
+    <row r="38" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H38" s="11"/>
+    </row>
+    <row r="39" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H39" s="11"/>
+    </row>
+    <row r="40" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H40" s="11"/>
+    </row>
+    <row r="41" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H41" s="11"/>
+    </row>
+    <row r="42" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H42" s="11"/>
+    </row>
+    <row r="43" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H43" s="11"/>
+    </row>
+    <row r="44" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H44" s="11"/>
+    </row>
+    <row r="45" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H45" s="11"/>
+    </row>
+    <row r="46" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H46" s="11"/>
+    </row>
+    <row r="47" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H47" s="11"/>
+    </row>
+    <row r="48" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H48" s="11"/>
+    </row>
+    <row r="49" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H49" s="11"/>
+    </row>
+    <row r="50" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H50" s="11"/>
+    </row>
+    <row r="51" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H51" s="11"/>
+    </row>
+    <row r="52" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H52" s="11"/>
+    </row>
+    <row r="53" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H53" s="11"/>
+    </row>
+    <row r="54" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H54" s="11"/>
+    </row>
+    <row r="55" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H55" s="11"/>
+    </row>
+    <row r="56" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H56" s="11"/>
+    </row>
+    <row r="57" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H57" s="11"/>
+    </row>
+    <row r="58" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H58" s="11"/>
+    </row>
+    <row r="59" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H59" s="11"/>
+    </row>
+    <row r="60" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H60" s="11"/>
+    </row>
+    <row r="61" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H61" s="11"/>
+    </row>
+    <row r="62" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H62" s="11"/>
+    </row>
+    <row r="63" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H63" s="11"/>
+    </row>
+    <row r="64" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H64" s="11"/>
+    </row>
+    <row r="65" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H65" s="11"/>
+    </row>
+    <row r="66" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H66" s="11"/>
+    </row>
+    <row r="67" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H67" s="11"/>
+    </row>
+    <row r="68" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H68" s="11"/>
+    </row>
+    <row r="69" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H69" s="11"/>
+    </row>
+    <row r="70" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H70" s="11"/>
+    </row>
+    <row r="71" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H71" s="11"/>
+    </row>
+    <row r="72" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H72" s="11"/>
+    </row>
+    <row r="73" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H73" s="11"/>
+    </row>
+    <row r="74" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H74" s="11"/>
+    </row>
+    <row r="75" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H75" s="11"/>
+    </row>
+    <row r="76" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H76" s="11"/>
+    </row>
+    <row r="77" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H77" s="11"/>
+    </row>
+    <row r="78" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H78" s="11"/>
+    </row>
+    <row r="79" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H79" s="11"/>
+    </row>
+    <row r="80" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H80" s="11"/>
+    </row>
+    <row r="81" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H81" s="11"/>
+    </row>
+    <row r="82" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H82" s="11"/>
+    </row>
+    <row r="83" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H83" s="11"/>
+    </row>
+    <row r="84" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H84" s="11"/>
+    </row>
+    <row r="85" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H85" s="11"/>
+    </row>
+    <row r="86" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H86" s="11"/>
+    </row>
+    <row r="87" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H87" s="11"/>
+    </row>
+    <row r="88" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H88" s="11"/>
+    </row>
+    <row r="89" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H89" s="11"/>
+    </row>
+    <row r="90" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H90" s="11"/>
+    </row>
+    <row r="91" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H91" s="11"/>
+    </row>
+    <row r="92" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H92" s="11"/>
+    </row>
+    <row r="93" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H93" s="11"/>
+    </row>
+    <row r="94" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H94" s="11"/>
+    </row>
+    <row r="95" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H95" s="11"/>
+    </row>
+    <row r="96" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H96" s="11"/>
+    </row>
+    <row r="97" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H97" s="11"/>
+    </row>
+    <row r="98" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H98" s="11"/>
+    </row>
+    <row r="99" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H99" s="11"/>
+    </row>
+    <row r="100" spans="8:8" x14ac:dyDescent="0.7">
+      <c r="H100" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="F11:F13"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="C11:C13"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="D11:D13"/>
     <mergeCell ref="E11:E13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="F11:F13"/>
     <mergeCell ref="G11:G13"/>
   </mergeCells>
   <conditionalFormatting sqref="F1:F13 F123:F1048576">

--- a/public/template_advance.xlsx
+++ b/public/template_advance.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\backend\financial_project\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\Financial-Project\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>ក្រសួងការងារ និងបណ្ដុះបណ្ដាលវិជ្ជាជីវៈ</t>
   </si>
@@ -57,28 +57,76 @@
     <t>ប្រចាំខែមិថុនា ឆ្នាំ២០២៤</t>
   </si>
   <si>
+    <t>ជំពូក</t>
+  </si>
+  <si>
+    <t>គណនី</t>
+  </si>
+  <si>
     <t>អនុគណនី</t>
   </si>
   <si>
     <t>លេខកូដកម្មវិធី</t>
   </si>
   <si>
+    <t>ចំណាត់ថ្នាក់</t>
+  </si>
+  <si>
     <t>ច្បាប់ហិ.វ</t>
   </si>
   <si>
+    <t>ឥណទានបច្ចុប្បន្ន</t>
+  </si>
+  <si>
+    <t>ចលនាឥណទាន</t>
+  </si>
+  <si>
     <t>ស្ថានភាពឥណទានថ្មី</t>
   </si>
   <si>
+    <t>សមតុល្យដើមគ្រា</t>
+  </si>
+  <si>
     <t>អនុវត្ត</t>
   </si>
   <si>
-    <t>បរិយាយ</t>
-  </si>
-  <si>
-    <t>ល.រ</t>
-  </si>
-  <si>
-    <t>ផ្សេងៗ</t>
+    <t>សមតុល្យចុងគ្រា</t>
+  </si>
+  <si>
+    <t>ឥណទាននៅសល់</t>
+  </si>
+  <si>
+    <t>%ប្រៀបធៀប</t>
+  </si>
+  <si>
+    <t>កើន</t>
+  </si>
+  <si>
+    <t>ថយ</t>
+  </si>
+  <si>
+    <t>%ច្បាប់</t>
+  </si>
+  <si>
+    <t>%ច្បាប់កែតម្រូវ</t>
+  </si>
+  <si>
+    <t>បំពេញបន្ថែម</t>
+  </si>
+  <si>
+    <t>សរុប</t>
+  </si>
+  <si>
+    <t>កើនផ្ទៃក្នុង</t>
+  </si>
+  <si>
+    <t>មិនបានគ្រោងទុក</t>
+  </si>
+  <si>
+    <t>វិចារណកម្ម</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -159,7 +207,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -219,51 +267,26 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -273,7 +296,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -283,7 +315,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -293,6 +334,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -303,36 +350,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -347,34 +380,53 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
       </font>
     </dxf>
   </dxfs>
@@ -688,472 +740,729 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
+  <dimension ref="A1:X100"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="24.5" x14ac:dyDescent="1"/>
   <cols>
-    <col min="1" max="1" width="7.875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="11" style="11"/>
-    <col min="3" max="3" width="14.375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="37.625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="25.875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="22.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" style="20" customWidth="1"/>
-    <col min="8" max="8" width="11" style="21"/>
+    <col min="1" max="1" width="7.83203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="11" style="20"/>
+    <col min="4" max="4" width="14.33203125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="22" customWidth="1"/>
+    <col min="6" max="7" width="25.83203125" style="17" customWidth="1"/>
+    <col min="8" max="8" width="16.5" style="17" customWidth="1"/>
+    <col min="9" max="10" width="15.83203125" style="17" customWidth="1"/>
+    <col min="11" max="12" width="12.83203125" style="17" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" style="18" customWidth="1"/>
+    <col min="14" max="15" width="20.83203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" style="17" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="17" customWidth="1"/>
+    <col min="18" max="18" width="15.58203125" style="18" customWidth="1"/>
+    <col min="19" max="19" width="13" style="33" customWidth="1"/>
+    <col min="20" max="20" width="13" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.35">
+      <c r="A1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="22"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="23"/>
-    </row>
-    <row r="3" spans="1:11" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="32">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" spans="1:24" ht="28" x14ac:dyDescent="0.35">
+      <c r="A3" s="37">
         <v>3</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="24"/>
-    </row>
-    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.7">
-      <c r="A4" s="14" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="5"/>
+    </row>
+    <row r="4" spans="1:24" ht="33" x14ac:dyDescent="1">
+      <c r="A4" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.7">
-      <c r="A5" s="14" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:24" ht="33" x14ac:dyDescent="1">
+      <c r="A5" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:11" ht="33" x14ac:dyDescent="0.7">
-      <c r="A6" s="14" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:24" ht="33" x14ac:dyDescent="1">
+      <c r="A6" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:11" ht="33" x14ac:dyDescent="0.7">
-      <c r="A7" s="14"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:11" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:24" ht="33" x14ac:dyDescent="1">
+      <c r="A7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="1">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:24" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="A10" s="29" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="1">
+      <c r="A10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="11"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H18" s="11"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H22" s="11"/>
-    </row>
-    <row r="23" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H23" s="11"/>
-    </row>
-    <row r="24" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H24" s="11"/>
-    </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H25" s="11"/>
-    </row>
-    <row r="26" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H26" s="11"/>
-    </row>
-    <row r="27" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H31" s="11"/>
-    </row>
-    <row r="32" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H38" s="11"/>
-    </row>
-    <row r="39" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H39" s="11"/>
-    </row>
-    <row r="40" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H40" s="11"/>
-    </row>
-    <row r="41" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H41" s="11"/>
-    </row>
-    <row r="42" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H42" s="11"/>
-    </row>
-    <row r="43" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H43" s="11"/>
-    </row>
-    <row r="44" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H44" s="11"/>
-    </row>
-    <row r="45" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H46" s="11"/>
-    </row>
-    <row r="47" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H47" s="11"/>
-    </row>
-    <row r="48" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H48" s="11"/>
-    </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H49" s="11"/>
-    </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H50" s="11"/>
-    </row>
-    <row r="51" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H51" s="11"/>
-    </row>
-    <row r="52" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H52" s="11"/>
-    </row>
-    <row r="53" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H53" s="11"/>
-    </row>
-    <row r="54" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H54" s="11"/>
-    </row>
-    <row r="55" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H55" s="11"/>
-    </row>
-    <row r="56" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H56" s="11"/>
-    </row>
-    <row r="57" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H57" s="11"/>
-    </row>
-    <row r="58" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H58" s="11"/>
-    </row>
-    <row r="59" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H59" s="11"/>
-    </row>
-    <row r="60" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H60" s="11"/>
-    </row>
-    <row r="61" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H61" s="11"/>
-    </row>
-    <row r="62" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H62" s="11"/>
-    </row>
-    <row r="63" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H63" s="11"/>
-    </row>
-    <row r="64" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H64" s="11"/>
-    </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H65" s="11"/>
-    </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H66" s="11"/>
-    </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H67" s="11"/>
-    </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H68" s="11"/>
-    </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H69" s="11"/>
-    </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H70" s="11"/>
-    </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H71" s="11"/>
-    </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H72" s="11"/>
-    </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H73" s="11"/>
-    </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H74" s="11"/>
-    </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H75" s="11"/>
-    </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H76" s="11"/>
-    </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H77" s="11"/>
-    </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H78" s="11"/>
-    </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H79" s="11"/>
-    </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H80" s="11"/>
-    </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H81" s="11"/>
-    </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H82" s="11"/>
-    </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H83" s="11"/>
-    </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H84" s="11"/>
-    </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H85" s="11"/>
-    </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H86" s="11"/>
-    </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H87" s="11"/>
-    </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H88" s="11"/>
-    </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H89" s="11"/>
-    </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H90" s="11"/>
-    </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H91" s="11"/>
-    </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H92" s="11"/>
-    </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H93" s="11"/>
-    </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H94" s="11"/>
-    </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H95" s="11"/>
-    </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H96" s="11"/>
-    </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H97" s="11"/>
-    </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H98" s="11"/>
-    </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H99" s="11"/>
-    </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.7">
-      <c r="H100" s="11"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="P11" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="S11" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" s="41"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12" s="39"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="45"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="T12" s="43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="49" x14ac:dyDescent="0.35">
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="40"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="43"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="1">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="17"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="1">
+      <c r="S15" s="32"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="1">
+      <c r="S16" s="32"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="19:21" x14ac:dyDescent="1">
+      <c r="S17" s="32"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="19:21" x14ac:dyDescent="1">
+      <c r="S18" s="32"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="19:21" x14ac:dyDescent="1">
+      <c r="S19" s="32"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="19:21" x14ac:dyDescent="1">
+      <c r="S20" s="32"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="19:21" x14ac:dyDescent="1">
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" spans="19:21" x14ac:dyDescent="1">
+      <c r="U22" s="1"/>
+    </row>
+    <row r="23" spans="19:21" x14ac:dyDescent="1">
+      <c r="U23" s="1"/>
+    </row>
+    <row r="24" spans="19:21" x14ac:dyDescent="1">
+      <c r="U24" s="1"/>
+    </row>
+    <row r="25" spans="19:21" x14ac:dyDescent="1">
+      <c r="U25" s="1"/>
+    </row>
+    <row r="26" spans="19:21" x14ac:dyDescent="1">
+      <c r="U26" s="1"/>
+    </row>
+    <row r="27" spans="19:21" x14ac:dyDescent="1">
+      <c r="U27" s="1"/>
+    </row>
+    <row r="28" spans="19:21" x14ac:dyDescent="1">
+      <c r="U28" s="1"/>
+    </row>
+    <row r="29" spans="19:21" x14ac:dyDescent="1">
+      <c r="U29" s="1"/>
+    </row>
+    <row r="30" spans="19:21" x14ac:dyDescent="1">
+      <c r="U30" s="1"/>
+    </row>
+    <row r="31" spans="19:21" x14ac:dyDescent="1">
+      <c r="U31" s="1"/>
+    </row>
+    <row r="32" spans="19:21" x14ac:dyDescent="1">
+      <c r="U32" s="1"/>
+    </row>
+    <row r="33" spans="21:21" x14ac:dyDescent="1">
+      <c r="U33" s="1"/>
+    </row>
+    <row r="34" spans="21:21" x14ac:dyDescent="1">
+      <c r="U34" s="1"/>
+    </row>
+    <row r="35" spans="21:21" x14ac:dyDescent="1">
+      <c r="U35" s="1"/>
+    </row>
+    <row r="36" spans="21:21" x14ac:dyDescent="1">
+      <c r="U36" s="1"/>
+    </row>
+    <row r="37" spans="21:21" x14ac:dyDescent="1">
+      <c r="U37" s="1"/>
+    </row>
+    <row r="38" spans="21:21" x14ac:dyDescent="1">
+      <c r="U38" s="1"/>
+    </row>
+    <row r="39" spans="21:21" x14ac:dyDescent="1">
+      <c r="U39" s="1"/>
+    </row>
+    <row r="40" spans="21:21" x14ac:dyDescent="1">
+      <c r="U40" s="1"/>
+    </row>
+    <row r="41" spans="21:21" x14ac:dyDescent="1">
+      <c r="U41" s="1"/>
+    </row>
+    <row r="42" spans="21:21" x14ac:dyDescent="1">
+      <c r="U42" s="1"/>
+    </row>
+    <row r="43" spans="21:21" x14ac:dyDescent="1">
+      <c r="U43" s="1"/>
+    </row>
+    <row r="44" spans="21:21" x14ac:dyDescent="1">
+      <c r="U44" s="1"/>
+    </row>
+    <row r="45" spans="21:21" x14ac:dyDescent="1">
+      <c r="U45" s="1"/>
+    </row>
+    <row r="46" spans="21:21" x14ac:dyDescent="1">
+      <c r="U46" s="1"/>
+    </row>
+    <row r="47" spans="21:21" x14ac:dyDescent="1">
+      <c r="U47" s="1"/>
+    </row>
+    <row r="48" spans="21:21" x14ac:dyDescent="1">
+      <c r="U48" s="1"/>
+    </row>
+    <row r="49" spans="21:21" x14ac:dyDescent="1">
+      <c r="U49" s="1"/>
+    </row>
+    <row r="50" spans="21:21" x14ac:dyDescent="1">
+      <c r="U50" s="1"/>
+    </row>
+    <row r="51" spans="21:21" x14ac:dyDescent="1">
+      <c r="U51" s="1"/>
+    </row>
+    <row r="52" spans="21:21" x14ac:dyDescent="1">
+      <c r="U52" s="1"/>
+    </row>
+    <row r="53" spans="21:21" x14ac:dyDescent="1">
+      <c r="U53" s="1"/>
+    </row>
+    <row r="54" spans="21:21" x14ac:dyDescent="1">
+      <c r="U54" s="1"/>
+    </row>
+    <row r="55" spans="21:21" x14ac:dyDescent="1">
+      <c r="U55" s="1"/>
+    </row>
+    <row r="56" spans="21:21" x14ac:dyDescent="1">
+      <c r="U56" s="1"/>
+    </row>
+    <row r="57" spans="21:21" x14ac:dyDescent="1">
+      <c r="U57" s="1"/>
+    </row>
+    <row r="58" spans="21:21" x14ac:dyDescent="1">
+      <c r="U58" s="1"/>
+    </row>
+    <row r="59" spans="21:21" x14ac:dyDescent="1">
+      <c r="U59" s="1"/>
+    </row>
+    <row r="60" spans="21:21" x14ac:dyDescent="1">
+      <c r="U60" s="1"/>
+    </row>
+    <row r="61" spans="21:21" x14ac:dyDescent="1">
+      <c r="U61" s="1"/>
+    </row>
+    <row r="62" spans="21:21" x14ac:dyDescent="1">
+      <c r="U62" s="1"/>
+    </row>
+    <row r="63" spans="21:21" x14ac:dyDescent="1">
+      <c r="U63" s="1"/>
+    </row>
+    <row r="64" spans="21:21" x14ac:dyDescent="1">
+      <c r="U64" s="1"/>
+    </row>
+    <row r="65" spans="21:21" x14ac:dyDescent="1">
+      <c r="U65" s="1"/>
+    </row>
+    <row r="66" spans="21:21" x14ac:dyDescent="1">
+      <c r="U66" s="1"/>
+    </row>
+    <row r="67" spans="21:21" x14ac:dyDescent="1">
+      <c r="U67" s="1"/>
+    </row>
+    <row r="68" spans="21:21" x14ac:dyDescent="1">
+      <c r="U68" s="1"/>
+    </row>
+    <row r="69" spans="21:21" x14ac:dyDescent="1">
+      <c r="U69" s="1"/>
+    </row>
+    <row r="70" spans="21:21" x14ac:dyDescent="1">
+      <c r="U70" s="1"/>
+    </row>
+    <row r="71" spans="21:21" x14ac:dyDescent="1">
+      <c r="U71" s="1"/>
+    </row>
+    <row r="72" spans="21:21" x14ac:dyDescent="1">
+      <c r="U72" s="1"/>
+    </row>
+    <row r="73" spans="21:21" x14ac:dyDescent="1">
+      <c r="U73" s="1"/>
+    </row>
+    <row r="74" spans="21:21" x14ac:dyDescent="1">
+      <c r="U74" s="1"/>
+    </row>
+    <row r="75" spans="21:21" x14ac:dyDescent="1">
+      <c r="U75" s="1"/>
+    </row>
+    <row r="76" spans="21:21" x14ac:dyDescent="1">
+      <c r="U76" s="1"/>
+    </row>
+    <row r="77" spans="21:21" x14ac:dyDescent="1">
+      <c r="U77" s="1"/>
+    </row>
+    <row r="78" spans="21:21" x14ac:dyDescent="1">
+      <c r="U78" s="1"/>
+    </row>
+    <row r="79" spans="21:21" x14ac:dyDescent="1">
+      <c r="U79" s="1"/>
+    </row>
+    <row r="80" spans="21:21" x14ac:dyDescent="1">
+      <c r="U80" s="1"/>
+    </row>
+    <row r="81" spans="21:21" x14ac:dyDescent="1">
+      <c r="U81" s="1"/>
+    </row>
+    <row r="82" spans="21:21" x14ac:dyDescent="1">
+      <c r="U82" s="1"/>
+    </row>
+    <row r="83" spans="21:21" x14ac:dyDescent="1">
+      <c r="U83" s="1"/>
+    </row>
+    <row r="84" spans="21:21" x14ac:dyDescent="1">
+      <c r="U84" s="1"/>
+    </row>
+    <row r="85" spans="21:21" x14ac:dyDescent="1">
+      <c r="U85" s="1"/>
+    </row>
+    <row r="86" spans="21:21" x14ac:dyDescent="1">
+      <c r="U86" s="1"/>
+    </row>
+    <row r="87" spans="21:21" x14ac:dyDescent="1">
+      <c r="U87" s="1"/>
+    </row>
+    <row r="88" spans="21:21" x14ac:dyDescent="1">
+      <c r="U88" s="1"/>
+    </row>
+    <row r="89" spans="21:21" x14ac:dyDescent="1">
+      <c r="U89" s="1"/>
+    </row>
+    <row r="90" spans="21:21" x14ac:dyDescent="1">
+      <c r="U90" s="1"/>
+    </row>
+    <row r="91" spans="21:21" x14ac:dyDescent="1">
+      <c r="U91" s="1"/>
+    </row>
+    <row r="92" spans="21:21" x14ac:dyDescent="1">
+      <c r="U92" s="1"/>
+    </row>
+    <row r="93" spans="21:21" x14ac:dyDescent="1">
+      <c r="U93" s="1"/>
+    </row>
+    <row r="94" spans="21:21" x14ac:dyDescent="1">
+      <c r="U94" s="1"/>
+    </row>
+    <row r="95" spans="21:21" x14ac:dyDescent="1">
+      <c r="U95" s="1"/>
+    </row>
+    <row r="96" spans="21:21" x14ac:dyDescent="1">
+      <c r="U96" s="1"/>
+    </row>
+    <row r="97" spans="21:21" x14ac:dyDescent="1">
+      <c r="U97" s="1"/>
+    </row>
+    <row r="98" spans="21:21" x14ac:dyDescent="1">
+      <c r="U98" s="1"/>
+    </row>
+    <row r="99" spans="21:21" x14ac:dyDescent="1">
+      <c r="U99" s="1"/>
+    </row>
+    <row r="100" spans="21:21" x14ac:dyDescent="1">
+      <c r="U100" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="H11:H13"/>
+  <mergeCells count="24">
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="O11:O13"/>
+    <mergeCell ref="M11:M13"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="C11:C13"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A9:G9"/>
     <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:L11"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="A10:T10"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A9:T9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F1:F13 F123:F1048576">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="T4:T8 T11:T1048576">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R1048576">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N13 N123:N1048576">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S1:S1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/template_advance.xlsx
+++ b/public/template_advance.xlsx
@@ -274,7 +274,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -302,12 +302,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -315,16 +309,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -337,9 +325,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -356,13 +341,25 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -389,10 +386,10 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -740,104 +737,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:X100"/>
+  <dimension ref="A1:X126"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="24.5" x14ac:dyDescent="1"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" style="20" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="11" style="20"/>
-    <col min="4" max="4" width="14.33203125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="37.58203125" style="22" customWidth="1"/>
-    <col min="6" max="7" width="25.83203125" style="17" customWidth="1"/>
-    <col min="8" max="8" width="16.5" style="17" customWidth="1"/>
-    <col min="9" max="10" width="15.83203125" style="17" customWidth="1"/>
-    <col min="11" max="12" width="12.83203125" style="17" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" style="18" customWidth="1"/>
-    <col min="14" max="15" width="20.83203125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" style="17" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" style="17" customWidth="1"/>
-    <col min="18" max="18" width="15.58203125" style="18" customWidth="1"/>
-    <col min="19" max="19" width="13" style="33" customWidth="1"/>
-    <col min="20" max="20" width="13" style="19" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="11" style="16"/>
+    <col min="4" max="4" width="14.33203125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="18" customWidth="1"/>
+    <col min="6" max="7" width="25.83203125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="16.5" style="14" customWidth="1"/>
+    <col min="9" max="10" width="15.83203125" style="14" customWidth="1"/>
+    <col min="11" max="12" width="12.83203125" style="14" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" style="15" customWidth="1"/>
+    <col min="14" max="15" width="20.83203125" style="14" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" style="14" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="14" customWidth="1"/>
+    <col min="18" max="18" width="15.58203125" style="15" customWidth="1"/>
+    <col min="19" max="19" width="13" style="30" customWidth="1"/>
+    <col min="20" max="20" width="13" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.35">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
       <c r="U1" s="2"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:24" ht="28" x14ac:dyDescent="0.35">
-      <c r="A3" s="37">
+      <c r="A3" s="36">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
       <c r="U3" s="5"/>
     </row>
     <row r="4" spans="1:24" ht="33" x14ac:dyDescent="1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="6"/>
@@ -857,12 +854,12 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="10"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
       <c r="U4" s="1"/>
     </row>
     <row r="5" spans="1:24" ht="33" x14ac:dyDescent="1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="6"/>
@@ -882,12 +879,12 @@
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="10"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="26"/>
       <c r="U5" s="1"/>
     </row>
     <row r="6" spans="1:24" ht="33" x14ac:dyDescent="1">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="20" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="6"/>
@@ -907,12 +904,12 @@
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="10"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
       <c r="U6" s="1"/>
     </row>
     <row r="7" spans="1:24" ht="33" x14ac:dyDescent="1">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="6"/>
@@ -932,16 +929,16 @@
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="10"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
       <c r="U7" s="1"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="1">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -955,469 +952,633 @@
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="10"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
       <c r="U8" s="1"/>
     </row>
     <row r="9" spans="1:24" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="1">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G11" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="45" t="s">
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="N11" s="40" t="s">
+      <c r="N11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="O11" s="40" t="s">
+      <c r="O11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="P11" s="40" t="s">
+      <c r="P11" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="Q11" s="40" t="s">
+      <c r="Q11" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="R11" s="45" t="s">
+      <c r="R11" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="S11" s="41" t="s">
+      <c r="S11" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="T11" s="41"/>
+      <c r="T11" s="40"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="40" t="s">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40" t="s">
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="45"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="42" t="s">
+      <c r="M12" s="44"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="T12" s="43" t="s">
+      <c r="T12" s="42" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="49" x14ac:dyDescent="0.35">
-      <c r="A13" s="39"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="23" t="s">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="K13" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="43"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="42"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="17"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="24"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="14"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="31"/>
       <c r="U14" s="1"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="1">
-      <c r="S15" s="32"/>
-      <c r="T15" s="24"/>
+      <c r="M15" s="14"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="31"/>
       <c r="U15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="1">
-      <c r="S16" s="32"/>
-      <c r="T16" s="24"/>
+      <c r="M16" s="14"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="31"/>
       <c r="U16" s="1"/>
     </row>
-    <row r="17" spans="19:21" x14ac:dyDescent="1">
-      <c r="S17" s="32"/>
-      <c r="T17" s="24"/>
+    <row r="17" spans="13:21" x14ac:dyDescent="1">
+      <c r="M17" s="14"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="31"/>
       <c r="U17" s="1"/>
     </row>
-    <row r="18" spans="19:21" x14ac:dyDescent="1">
-      <c r="S18" s="32"/>
-      <c r="T18" s="24"/>
+    <row r="18" spans="13:21" x14ac:dyDescent="1">
+      <c r="M18" s="14"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="31"/>
       <c r="U18" s="1"/>
     </row>
-    <row r="19" spans="19:21" x14ac:dyDescent="1">
-      <c r="S19" s="32"/>
-      <c r="T19" s="24"/>
+    <row r="19" spans="13:21" x14ac:dyDescent="1">
+      <c r="M19" s="14"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="31"/>
       <c r="U19" s="1"/>
     </row>
-    <row r="20" spans="19:21" x14ac:dyDescent="1">
-      <c r="S20" s="32"/>
-      <c r="T20" s="24"/>
+    <row r="20" spans="13:21" x14ac:dyDescent="1">
+      <c r="M20" s="14"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="31"/>
       <c r="U20" s="1"/>
     </row>
-    <row r="21" spans="19:21" x14ac:dyDescent="1">
+    <row r="21" spans="13:21" x14ac:dyDescent="1">
+      <c r="M21" s="14"/>
       <c r="U21" s="1"/>
     </row>
-    <row r="22" spans="19:21" x14ac:dyDescent="1">
+    <row r="22" spans="13:21" x14ac:dyDescent="1">
+      <c r="M22" s="14"/>
       <c r="U22" s="1"/>
     </row>
-    <row r="23" spans="19:21" x14ac:dyDescent="1">
+    <row r="23" spans="13:21" x14ac:dyDescent="1">
+      <c r="M23" s="14"/>
       <c r="U23" s="1"/>
     </row>
-    <row r="24" spans="19:21" x14ac:dyDescent="1">
+    <row r="24" spans="13:21" x14ac:dyDescent="1">
+      <c r="M24" s="14"/>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" spans="19:21" x14ac:dyDescent="1">
+    <row r="25" spans="13:21" x14ac:dyDescent="1">
+      <c r="M25" s="14"/>
       <c r="U25" s="1"/>
     </row>
-    <row r="26" spans="19:21" x14ac:dyDescent="1">
+    <row r="26" spans="13:21" x14ac:dyDescent="1">
+      <c r="M26" s="14"/>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" spans="19:21" x14ac:dyDescent="1">
+    <row r="27" spans="13:21" x14ac:dyDescent="1">
+      <c r="M27" s="14"/>
       <c r="U27" s="1"/>
     </row>
-    <row r="28" spans="19:21" x14ac:dyDescent="1">
+    <row r="28" spans="13:21" x14ac:dyDescent="1">
+      <c r="M28" s="14"/>
       <c r="U28" s="1"/>
     </row>
-    <row r="29" spans="19:21" x14ac:dyDescent="1">
+    <row r="29" spans="13:21" x14ac:dyDescent="1">
+      <c r="M29" s="14"/>
       <c r="U29" s="1"/>
     </row>
-    <row r="30" spans="19:21" x14ac:dyDescent="1">
+    <row r="30" spans="13:21" x14ac:dyDescent="1">
+      <c r="M30" s="14"/>
       <c r="U30" s="1"/>
     </row>
-    <row r="31" spans="19:21" x14ac:dyDescent="1">
+    <row r="31" spans="13:21" x14ac:dyDescent="1">
+      <c r="M31" s="14"/>
       <c r="U31" s="1"/>
     </row>
-    <row r="32" spans="19:21" x14ac:dyDescent="1">
+    <row r="32" spans="13:21" x14ac:dyDescent="1">
+      <c r="M32" s="14"/>
       <c r="U32" s="1"/>
     </row>
-    <row r="33" spans="21:21" x14ac:dyDescent="1">
+    <row r="33" spans="13:21" x14ac:dyDescent="1">
+      <c r="M33" s="14"/>
       <c r="U33" s="1"/>
     </row>
-    <row r="34" spans="21:21" x14ac:dyDescent="1">
+    <row r="34" spans="13:21" x14ac:dyDescent="1">
+      <c r="M34" s="14"/>
       <c r="U34" s="1"/>
     </row>
-    <row r="35" spans="21:21" x14ac:dyDescent="1">
+    <row r="35" spans="13:21" x14ac:dyDescent="1">
+      <c r="M35" s="14"/>
       <c r="U35" s="1"/>
     </row>
-    <row r="36" spans="21:21" x14ac:dyDescent="1">
+    <row r="36" spans="13:21" x14ac:dyDescent="1">
+      <c r="M36" s="14"/>
       <c r="U36" s="1"/>
     </row>
-    <row r="37" spans="21:21" x14ac:dyDescent="1">
+    <row r="37" spans="13:21" x14ac:dyDescent="1">
+      <c r="M37" s="14"/>
       <c r="U37" s="1"/>
     </row>
-    <row r="38" spans="21:21" x14ac:dyDescent="1">
+    <row r="38" spans="13:21" x14ac:dyDescent="1">
+      <c r="M38" s="14"/>
       <c r="U38" s="1"/>
     </row>
-    <row r="39" spans="21:21" x14ac:dyDescent="1">
+    <row r="39" spans="13:21" x14ac:dyDescent="1">
+      <c r="M39" s="14"/>
       <c r="U39" s="1"/>
     </row>
-    <row r="40" spans="21:21" x14ac:dyDescent="1">
+    <row r="40" spans="13:21" x14ac:dyDescent="1">
+      <c r="M40" s="14"/>
       <c r="U40" s="1"/>
     </row>
-    <row r="41" spans="21:21" x14ac:dyDescent="1">
+    <row r="41" spans="13:21" x14ac:dyDescent="1">
+      <c r="M41" s="14"/>
       <c r="U41" s="1"/>
     </row>
-    <row r="42" spans="21:21" x14ac:dyDescent="1">
+    <row r="42" spans="13:21" x14ac:dyDescent="1">
+      <c r="M42" s="14"/>
       <c r="U42" s="1"/>
     </row>
-    <row r="43" spans="21:21" x14ac:dyDescent="1">
+    <row r="43" spans="13:21" x14ac:dyDescent="1">
+      <c r="M43" s="14"/>
       <c r="U43" s="1"/>
     </row>
-    <row r="44" spans="21:21" x14ac:dyDescent="1">
+    <row r="44" spans="13:21" x14ac:dyDescent="1">
+      <c r="M44" s="14"/>
       <c r="U44" s="1"/>
     </row>
-    <row r="45" spans="21:21" x14ac:dyDescent="1">
+    <row r="45" spans="13:21" x14ac:dyDescent="1">
+      <c r="M45" s="14"/>
       <c r="U45" s="1"/>
     </row>
-    <row r="46" spans="21:21" x14ac:dyDescent="1">
+    <row r="46" spans="13:21" x14ac:dyDescent="1">
+      <c r="M46" s="14"/>
       <c r="U46" s="1"/>
     </row>
-    <row r="47" spans="21:21" x14ac:dyDescent="1">
+    <row r="47" spans="13:21" x14ac:dyDescent="1">
+      <c r="M47" s="14"/>
       <c r="U47" s="1"/>
     </row>
-    <row r="48" spans="21:21" x14ac:dyDescent="1">
+    <row r="48" spans="13:21" x14ac:dyDescent="1">
+      <c r="M48" s="14"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" spans="21:21" x14ac:dyDescent="1">
+    <row r="49" spans="13:21" x14ac:dyDescent="1">
+      <c r="M49" s="14"/>
       <c r="U49" s="1"/>
     </row>
-    <row r="50" spans="21:21" x14ac:dyDescent="1">
+    <row r="50" spans="13:21" x14ac:dyDescent="1">
+      <c r="M50" s="14"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" spans="21:21" x14ac:dyDescent="1">
+    <row r="51" spans="13:21" x14ac:dyDescent="1">
+      <c r="M51" s="14"/>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" spans="21:21" x14ac:dyDescent="1">
+    <row r="52" spans="13:21" x14ac:dyDescent="1">
+      <c r="M52" s="14"/>
       <c r="U52" s="1"/>
     </row>
-    <row r="53" spans="21:21" x14ac:dyDescent="1">
+    <row r="53" spans="13:21" x14ac:dyDescent="1">
+      <c r="M53" s="14"/>
       <c r="U53" s="1"/>
     </row>
-    <row r="54" spans="21:21" x14ac:dyDescent="1">
+    <row r="54" spans="13:21" x14ac:dyDescent="1">
+      <c r="M54" s="14"/>
       <c r="U54" s="1"/>
     </row>
-    <row r="55" spans="21:21" x14ac:dyDescent="1">
+    <row r="55" spans="13:21" x14ac:dyDescent="1">
+      <c r="M55" s="14"/>
       <c r="U55" s="1"/>
     </row>
-    <row r="56" spans="21:21" x14ac:dyDescent="1">
+    <row r="56" spans="13:21" x14ac:dyDescent="1">
+      <c r="M56" s="14"/>
       <c r="U56" s="1"/>
     </row>
-    <row r="57" spans="21:21" x14ac:dyDescent="1">
+    <row r="57" spans="13:21" x14ac:dyDescent="1">
+      <c r="M57" s="14"/>
       <c r="U57" s="1"/>
     </row>
-    <row r="58" spans="21:21" x14ac:dyDescent="1">
+    <row r="58" spans="13:21" x14ac:dyDescent="1">
+      <c r="M58" s="14"/>
       <c r="U58" s="1"/>
     </row>
-    <row r="59" spans="21:21" x14ac:dyDescent="1">
+    <row r="59" spans="13:21" x14ac:dyDescent="1">
+      <c r="M59" s="14"/>
       <c r="U59" s="1"/>
     </row>
-    <row r="60" spans="21:21" x14ac:dyDescent="1">
+    <row r="60" spans="13:21" x14ac:dyDescent="1">
+      <c r="M60" s="14"/>
       <c r="U60" s="1"/>
     </row>
-    <row r="61" spans="21:21" x14ac:dyDescent="1">
+    <row r="61" spans="13:21" x14ac:dyDescent="1">
+      <c r="M61" s="14"/>
       <c r="U61" s="1"/>
     </row>
-    <row r="62" spans="21:21" x14ac:dyDescent="1">
+    <row r="62" spans="13:21" x14ac:dyDescent="1">
+      <c r="M62" s="14"/>
       <c r="U62" s="1"/>
     </row>
-    <row r="63" spans="21:21" x14ac:dyDescent="1">
+    <row r="63" spans="13:21" x14ac:dyDescent="1">
+      <c r="M63" s="14"/>
       <c r="U63" s="1"/>
     </row>
-    <row r="64" spans="21:21" x14ac:dyDescent="1">
+    <row r="64" spans="13:21" x14ac:dyDescent="1">
+      <c r="M64" s="14"/>
       <c r="U64" s="1"/>
     </row>
-    <row r="65" spans="21:21" x14ac:dyDescent="1">
+    <row r="65" spans="13:21" x14ac:dyDescent="1">
+      <c r="M65" s="14"/>
       <c r="U65" s="1"/>
     </row>
-    <row r="66" spans="21:21" x14ac:dyDescent="1">
+    <row r="66" spans="13:21" x14ac:dyDescent="1">
+      <c r="M66" s="14"/>
       <c r="U66" s="1"/>
     </row>
-    <row r="67" spans="21:21" x14ac:dyDescent="1">
+    <row r="67" spans="13:21" x14ac:dyDescent="1">
+      <c r="M67" s="14"/>
       <c r="U67" s="1"/>
     </row>
-    <row r="68" spans="21:21" x14ac:dyDescent="1">
+    <row r="68" spans="13:21" x14ac:dyDescent="1">
+      <c r="M68" s="14"/>
       <c r="U68" s="1"/>
     </row>
-    <row r="69" spans="21:21" x14ac:dyDescent="1">
+    <row r="69" spans="13:21" x14ac:dyDescent="1">
+      <c r="M69" s="14"/>
       <c r="U69" s="1"/>
     </row>
-    <row r="70" spans="21:21" x14ac:dyDescent="1">
+    <row r="70" spans="13:21" x14ac:dyDescent="1">
+      <c r="M70" s="14"/>
       <c r="U70" s="1"/>
     </row>
-    <row r="71" spans="21:21" x14ac:dyDescent="1">
+    <row r="71" spans="13:21" x14ac:dyDescent="1">
+      <c r="M71" s="14"/>
       <c r="U71" s="1"/>
     </row>
-    <row r="72" spans="21:21" x14ac:dyDescent="1">
+    <row r="72" spans="13:21" x14ac:dyDescent="1">
+      <c r="M72" s="14"/>
       <c r="U72" s="1"/>
     </row>
-    <row r="73" spans="21:21" x14ac:dyDescent="1">
+    <row r="73" spans="13:21" x14ac:dyDescent="1">
+      <c r="M73" s="14"/>
       <c r="U73" s="1"/>
     </row>
-    <row r="74" spans="21:21" x14ac:dyDescent="1">
+    <row r="74" spans="13:21" x14ac:dyDescent="1">
+      <c r="M74" s="14"/>
       <c r="U74" s="1"/>
     </row>
-    <row r="75" spans="21:21" x14ac:dyDescent="1">
+    <row r="75" spans="13:21" x14ac:dyDescent="1">
+      <c r="M75" s="14"/>
       <c r="U75" s="1"/>
     </row>
-    <row r="76" spans="21:21" x14ac:dyDescent="1">
+    <row r="76" spans="13:21" x14ac:dyDescent="1">
+      <c r="M76" s="14"/>
       <c r="U76" s="1"/>
     </row>
-    <row r="77" spans="21:21" x14ac:dyDescent="1">
+    <row r="77" spans="13:21" x14ac:dyDescent="1">
+      <c r="M77" s="14"/>
       <c r="U77" s="1"/>
     </row>
-    <row r="78" spans="21:21" x14ac:dyDescent="1">
+    <row r="78" spans="13:21" x14ac:dyDescent="1">
+      <c r="M78" s="14"/>
       <c r="U78" s="1"/>
     </row>
-    <row r="79" spans="21:21" x14ac:dyDescent="1">
+    <row r="79" spans="13:21" x14ac:dyDescent="1">
+      <c r="M79" s="14"/>
       <c r="U79" s="1"/>
     </row>
-    <row r="80" spans="21:21" x14ac:dyDescent="1">
+    <row r="80" spans="13:21" x14ac:dyDescent="1">
+      <c r="M80" s="14"/>
       <c r="U80" s="1"/>
     </row>
-    <row r="81" spans="21:21" x14ac:dyDescent="1">
+    <row r="81" spans="13:21" x14ac:dyDescent="1">
+      <c r="M81" s="14"/>
       <c r="U81" s="1"/>
     </row>
-    <row r="82" spans="21:21" x14ac:dyDescent="1">
+    <row r="82" spans="13:21" x14ac:dyDescent="1">
+      <c r="M82" s="14"/>
       <c r="U82" s="1"/>
     </row>
-    <row r="83" spans="21:21" x14ac:dyDescent="1">
+    <row r="83" spans="13:21" x14ac:dyDescent="1">
+      <c r="M83" s="14"/>
       <c r="U83" s="1"/>
     </row>
-    <row r="84" spans="21:21" x14ac:dyDescent="1">
+    <row r="84" spans="13:21" x14ac:dyDescent="1">
+      <c r="M84" s="14"/>
       <c r="U84" s="1"/>
     </row>
-    <row r="85" spans="21:21" x14ac:dyDescent="1">
+    <row r="85" spans="13:21" x14ac:dyDescent="1">
+      <c r="M85" s="14"/>
       <c r="U85" s="1"/>
     </row>
-    <row r="86" spans="21:21" x14ac:dyDescent="1">
+    <row r="86" spans="13:21" x14ac:dyDescent="1">
+      <c r="M86" s="14"/>
       <c r="U86" s="1"/>
     </row>
-    <row r="87" spans="21:21" x14ac:dyDescent="1">
+    <row r="87" spans="13:21" x14ac:dyDescent="1">
+      <c r="M87" s="14"/>
       <c r="U87" s="1"/>
     </row>
-    <row r="88" spans="21:21" x14ac:dyDescent="1">
+    <row r="88" spans="13:21" x14ac:dyDescent="1">
+      <c r="M88" s="14"/>
       <c r="U88" s="1"/>
     </row>
-    <row r="89" spans="21:21" x14ac:dyDescent="1">
+    <row r="89" spans="13:21" x14ac:dyDescent="1">
+      <c r="M89" s="14"/>
       <c r="U89" s="1"/>
     </row>
-    <row r="90" spans="21:21" x14ac:dyDescent="1">
+    <row r="90" spans="13:21" x14ac:dyDescent="1">
+      <c r="M90" s="14"/>
       <c r="U90" s="1"/>
     </row>
-    <row r="91" spans="21:21" x14ac:dyDescent="1">
+    <row r="91" spans="13:21" x14ac:dyDescent="1">
+      <c r="M91" s="14"/>
       <c r="U91" s="1"/>
     </row>
-    <row r="92" spans="21:21" x14ac:dyDescent="1">
+    <row r="92" spans="13:21" x14ac:dyDescent="1">
+      <c r="M92" s="14"/>
       <c r="U92" s="1"/>
     </row>
-    <row r="93" spans="21:21" x14ac:dyDescent="1">
+    <row r="93" spans="13:21" x14ac:dyDescent="1">
+      <c r="M93" s="14"/>
       <c r="U93" s="1"/>
     </row>
-    <row r="94" spans="21:21" x14ac:dyDescent="1">
+    <row r="94" spans="13:21" x14ac:dyDescent="1">
+      <c r="M94" s="14"/>
       <c r="U94" s="1"/>
     </row>
-    <row r="95" spans="21:21" x14ac:dyDescent="1">
+    <row r="95" spans="13:21" x14ac:dyDescent="1">
+      <c r="M95" s="14"/>
       <c r="U95" s="1"/>
     </row>
-    <row r="96" spans="21:21" x14ac:dyDescent="1">
+    <row r="96" spans="13:21" x14ac:dyDescent="1">
+      <c r="M96" s="14"/>
       <c r="U96" s="1"/>
     </row>
-    <row r="97" spans="21:21" x14ac:dyDescent="1">
+    <row r="97" spans="13:21" x14ac:dyDescent="1">
+      <c r="M97" s="14"/>
       <c r="U97" s="1"/>
     </row>
-    <row r="98" spans="21:21" x14ac:dyDescent="1">
+    <row r="98" spans="13:21" x14ac:dyDescent="1">
+      <c r="M98" s="14"/>
       <c r="U98" s="1"/>
     </row>
-    <row r="99" spans="21:21" x14ac:dyDescent="1">
+    <row r="99" spans="13:21" x14ac:dyDescent="1">
+      <c r="M99" s="14"/>
       <c r="U99" s="1"/>
     </row>
-    <row r="100" spans="21:21" x14ac:dyDescent="1">
+    <row r="100" spans="13:21" x14ac:dyDescent="1">
+      <c r="M100" s="14"/>
       <c r="U100" s="1"/>
+    </row>
+    <row r="101" spans="13:21" x14ac:dyDescent="1">
+      <c r="M101" s="14"/>
+    </row>
+    <row r="102" spans="13:21" x14ac:dyDescent="1">
+      <c r="M102" s="14"/>
+    </row>
+    <row r="103" spans="13:21" x14ac:dyDescent="1">
+      <c r="M103" s="14"/>
+    </row>
+    <row r="104" spans="13:21" x14ac:dyDescent="1">
+      <c r="M104" s="14"/>
+    </row>
+    <row r="105" spans="13:21" x14ac:dyDescent="1">
+      <c r="M105" s="14"/>
+    </row>
+    <row r="106" spans="13:21" x14ac:dyDescent="1">
+      <c r="M106" s="14"/>
+    </row>
+    <row r="107" spans="13:21" x14ac:dyDescent="1">
+      <c r="M107" s="14"/>
+    </row>
+    <row r="108" spans="13:21" x14ac:dyDescent="1">
+      <c r="M108" s="14"/>
+    </row>
+    <row r="109" spans="13:21" x14ac:dyDescent="1">
+      <c r="M109" s="14"/>
+    </row>
+    <row r="110" spans="13:21" x14ac:dyDescent="1">
+      <c r="M110" s="14"/>
+    </row>
+    <row r="111" spans="13:21" x14ac:dyDescent="1">
+      <c r="M111" s="14"/>
+    </row>
+    <row r="112" spans="13:21" x14ac:dyDescent="1">
+      <c r="M112" s="14"/>
+    </row>
+    <row r="113" spans="13:13" x14ac:dyDescent="1">
+      <c r="M113" s="14"/>
+    </row>
+    <row r="114" spans="13:13" x14ac:dyDescent="1">
+      <c r="M114" s="14"/>
+    </row>
+    <row r="115" spans="13:13" x14ac:dyDescent="1">
+      <c r="M115" s="14"/>
+    </row>
+    <row r="116" spans="13:13" x14ac:dyDescent="1">
+      <c r="M116" s="14"/>
+    </row>
+    <row r="117" spans="13:13" x14ac:dyDescent="1">
+      <c r="M117" s="14"/>
+    </row>
+    <row r="118" spans="13:13" x14ac:dyDescent="1">
+      <c r="M118" s="14"/>
+    </row>
+    <row r="119" spans="13:13" x14ac:dyDescent="1">
+      <c r="M119" s="14"/>
+    </row>
+    <row r="120" spans="13:13" x14ac:dyDescent="1">
+      <c r="M120" s="14"/>
+    </row>
+    <row r="121" spans="13:13" x14ac:dyDescent="1">
+      <c r="M121" s="14"/>
+    </row>
+    <row r="122" spans="13:13" x14ac:dyDescent="1">
+      <c r="M122" s="14"/>
+    </row>
+    <row r="123" spans="13:13" x14ac:dyDescent="1">
+      <c r="M123" s="14"/>
+    </row>
+    <row r="124" spans="13:13" x14ac:dyDescent="1">
+      <c r="M124" s="14"/>
+    </row>
+    <row r="125" spans="13:13" x14ac:dyDescent="1">
+      <c r="M125" s="14"/>
+    </row>
+    <row r="126" spans="13:13" x14ac:dyDescent="1">
+      <c r="M126" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="24">
